--- a/sofiback/public/preparacion.xlsx
+++ b/sofiback/public/preparacion.xlsx
@@ -16,8 +16,6 @@
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="A" localSheetId="0">hoja1!$VTV$1</definedName>
-    <definedName name="A">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">hoja1!$A$1:$AD$96</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
